--- a/artfynd/A 11330-2025 artfynd.xlsx
+++ b/artfynd/A 11330-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133591210</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133591206</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,8 +1044,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133591215</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 11330-2025 artfynd.xlsx
+++ b/artfynd/A 11330-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133591210</v>
+        <v>136186094</v>
       </c>
       <c r="B2" t="n">
-        <v>57912</v>
+        <v>57979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100082</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -717,7 +717,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -757,22 +757,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,43 +798,43 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133591210</t>
+          <t>https://artportalen.se/Sighting/136186094</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133591206</v>
+        <v>136186091</v>
       </c>
       <c r="B3" t="n">
-        <v>57391</v>
+        <v>57287</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102961</v>
+        <v>100065</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -881,22 +881,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,16 +922,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133591206</t>
+          <t>https://artportalen.se/Sighting/136186091</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133591215</v>
+        <v>133591210</v>
       </c>
       <c r="B4" t="n">
-        <v>58485</v>
+        <v>57912</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102995</v>
+        <v>100082</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -958,14 +958,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,7 +1046,875 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/133591210</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133591206</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57391</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102961</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Drillsnäppa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Actitis hypoleucos</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Brårud, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>339036</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6611887</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Järnskog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Patric Gullström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Patric Gullström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133591206</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136186102</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102980</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ladusvala</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hirundo rustica</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Brårud, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>339036</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6611887</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Järnskog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Patric Gullström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Patric Gullström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136186102</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136186109</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58526</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Brårud, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>339036</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6611887</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Järnskog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Patric Gullström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Patric Gullström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136186109</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133591215</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58485</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102995</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Buskskvätta</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Saxicola rubetra</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Brårud, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>339036</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6611887</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Järnskog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patric Gullström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patric Gullström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/133591215</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136186101</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Brårud, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>339036</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6611887</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Järnskog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patric Gullström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patric Gullström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136186101</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136186112</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58603</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Brårud, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>339036</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6611887</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Järnskog</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patric Gullström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patric Gullström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136186112</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136186115</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58705</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Brårud, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>339036</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6611887</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Järnskog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patric Gullström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patric Gullström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136186115</t>
         </is>
       </c>
     </row>
@@ -1055,6 +1923,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11330-2025 artfynd.xlsx
+++ b/artfynd/A 11330-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136186094</v>
       </c>
       <c r="B2" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>136186091</v>
       </c>
       <c r="B3" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>136186102</v>
       </c>
       <c r="B6" t="n">
-        <v>58238</v>
+        <v>58239</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>136186109</v>
       </c>
       <c r="B7" t="n">
-        <v>58526</v>
+        <v>58527</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136186101</v>
       </c>
       <c r="B9" t="n">
-        <v>58141</v>
+        <v>58142</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>136186112</v>
       </c>
       <c r="B10" t="n">
-        <v>58603</v>
+        <v>58604</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>136186115</v>
       </c>
       <c r="B11" t="n">
-        <v>58705</v>
+        <v>58706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 11330-2025 artfynd.xlsx
+++ b/artfynd/A 11330-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136186094</v>
       </c>
       <c r="B2" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>136186091</v>
       </c>
       <c r="B3" t="n">
-        <v>57288</v>
+        <v>57292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>136186102</v>
       </c>
       <c r="B6" t="n">
-        <v>58239</v>
+        <v>58243</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>136186109</v>
       </c>
       <c r="B7" t="n">
-        <v>58527</v>
+        <v>58531</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136186101</v>
       </c>
       <c r="B9" t="n">
-        <v>58142</v>
+        <v>58146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>136186112</v>
       </c>
       <c r="B10" t="n">
-        <v>58604</v>
+        <v>58608</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>136186115</v>
       </c>
       <c r="B11" t="n">
-        <v>58706</v>
+        <v>58710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 11330-2025 artfynd.xlsx
+++ b/artfynd/A 11330-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136186094</v>
       </c>
       <c r="B2" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>136186091</v>
       </c>
       <c r="B3" t="n">
-        <v>57292</v>
+        <v>57293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>136186102</v>
       </c>
       <c r="B6" t="n">
-        <v>58243</v>
+        <v>58244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>136186109</v>
       </c>
       <c r="B7" t="n">
-        <v>58531</v>
+        <v>58532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136186101</v>
       </c>
       <c r="B9" t="n">
-        <v>58146</v>
+        <v>58147</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>136186112</v>
       </c>
       <c r="B10" t="n">
-        <v>58608</v>
+        <v>58609</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>136186115</v>
       </c>
       <c r="B11" t="n">
-        <v>58710</v>
+        <v>58711</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 11330-2025 artfynd.xlsx
+++ b/artfynd/A 11330-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136186094</v>
       </c>
       <c r="B2" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>136186091</v>
       </c>
       <c r="B3" t="n">
-        <v>57293</v>
+        <v>57298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>136186102</v>
       </c>
       <c r="B6" t="n">
-        <v>58244</v>
+        <v>58249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>136186109</v>
       </c>
       <c r="B7" t="n">
-        <v>58532</v>
+        <v>58537</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136186101</v>
       </c>
       <c r="B9" t="n">
-        <v>58147</v>
+        <v>58152</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>136186112</v>
       </c>
       <c r="B10" t="n">
-        <v>58609</v>
+        <v>58614</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>136186115</v>
       </c>
       <c r="B11" t="n">
-        <v>58711</v>
+        <v>58716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 11330-2025 artfynd.xlsx
+++ b/artfynd/A 11330-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136186094</v>
       </c>
       <c r="B2" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>136186091</v>
       </c>
       <c r="B3" t="n">
-        <v>57298</v>
+        <v>57311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>136186102</v>
       </c>
       <c r="B6" t="n">
-        <v>58249</v>
+        <v>58262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>136186109</v>
       </c>
       <c r="B7" t="n">
-        <v>58537</v>
+        <v>58550</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136186101</v>
       </c>
       <c r="B9" t="n">
-        <v>58152</v>
+        <v>58165</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>136186112</v>
       </c>
       <c r="B10" t="n">
-        <v>58614</v>
+        <v>58627</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>136186115</v>
       </c>
       <c r="B11" t="n">
-        <v>58716</v>
+        <v>58729</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
